--- a/docs/设计概念选择.xlsx
+++ b/docs/设计概念选择.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/boywu/Desktop/架构作业1/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\dev\MapCollector\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C56D4991-80A0-924B-9062-F216ED173362}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{932373D7-C468-482C-8EC3-233C47483C9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14560" yWindow="1960" windowWidth="28040" windowHeight="17360" xr2:uid="{44F6DC92-3AE2-2C48-8048-599D73AA657E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{44F6DC92-3AE2-2C48-8048-599D73AA657E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>设计方案选择</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -49,10 +49,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>权衡</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>性能</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -66,14 +62,6 @@
   </si>
   <si>
     <t>sidebar</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>主选</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>适用微服务</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -145,7 +133,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -509,132 +497,121 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2B9C401-4677-F042-983B-BA87A298C754}">
   <dimension ref="A1:C16"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="51" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="1"/>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="2" t="s">
+      <c r="B3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>
       <c r="B4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="2"/>
       <c r="B5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="2" t="s">
-        <v>10</v>
-      </c>
       <c r="B6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="2"/>
       <c r="B7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="2"/>
       <c r="B8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="2"/>
       <c r="B9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="2"/>
       <c r="B11" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B12" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="2"/>
       <c r="B13" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="2"/>
       <c r="B14" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="1" t="s">
+      <c r="B16" t="s">
         <v>22</v>
-      </c>
-      <c r="B15" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B16" t="s">
-        <v>25</v>
       </c>
     </row>
   </sheetData>
